--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-specimen-common.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-specimen-common.xlsx
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Role[classCode=SPEC]</t>
@@ -307,13 +307,13 @@
     <t>リソースに関するメタデータ</t>
   </si>
   <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -350,7 +350,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -370,16 +370,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Specimen.meta.versionId</t>
   </si>
   <si>
-    <t>バージョン固有の識別子</t>
-  </si>
-  <si>
-    <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
   </si>
   <si>
     <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
@@ -399,7 +399,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースのバージョンが最後に変更されたとき」</t>
+    <t>リソースのバージョンが最後に変更されたとき</t>
   </si>
   <si>
     <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
@@ -424,8 +424,8 @@
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
   </si>
   <si>
-    <t>「プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
-この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。」</t>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。</t>
   </si>
   <si>
     <t>Meta.source</t>
@@ -493,7 +493,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「様々なタグを表すコードで、一般的にはワークフローに関連しています。</t>
+    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/common-tags</t>
@@ -609,7 +609,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -650,7 +650,7 @@
     <t>検査部門で採番された識別子</t>
   </si>
   <si>
-    <t>試験片を加速するときにラボによって割り当てられた識別子。これは、ローカルラボの手順に応じて、必ずしも試料識別子と同じではありません。 / The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
+    <t>試験片を加速するときにラボによって割り当てられたidentifier。これは、ローカルラボのプロシジャー（処置等）に応じて、必ずしも試料identifierと同じではありません。 / The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].act[classCode=ACSN, moodCode=EVN].id</t>
@@ -927,7 +927,7 @@
     <t>検体採取方法</t>
   </si>
   <si>
-    <t>手順の実行に使用される手法を指定するコード化された値。 / A coded value specifying the technique that is used to perform the procedure.</t>
+    <t>プロシジャー（処置等）の実行に使用される手法を指定するコード化された値。 / A coded value specifying the technique that is used to perform the procedure.</t>
   </si>
   <si>
     <t>採取方法</t>
@@ -1018,7 +1018,7 @@
     <t>手順のテキストによる説明</t>
   </si>
   <si>
-    <t>手順のテキスト説明。 / Textual description of procedure.</t>
+    <t>プロシジャー（処置等）のテキスト説明。 / Textual description of procedure.</t>
   </si>
   <si>
     <t>.text</t>
@@ -1030,7 +1030,7 @@
     <t>検体に適用される処理</t>
   </si>
   <si>
-    <t>試料の処理に使用される手順を指定するコード化された値。 / A coded value specifying the procedure used to process the specimen.</t>
+    <t>試料の処理に使用されるプロシジャー（処置等）を指定するコード化された値。 / A coded value specifying the procedure used to process the specimen.</t>
   </si>
   <si>
     <t>材料に対する処理</t>
@@ -1094,7 +1094,7 @@
     <t>採取容器のID</t>
   </si>
   <si>
-    <t>コンテナ用のID。複数があるかもしれません。メーカーのバーコード、ラボに割り当てられた識別子など。コンテナIDは、状況によっては試料IDとは異なる場合があります。 / Id for container. There may be multiple; a manufacturer's bar code, lab assigned identifier, etc. The container ID may differ from the specimen id in some circumstances.</t>
+    <t>コンテナ用のID。複数があるかもしれません。メーカーのバーコード、ラボに割り当てられたidentifierなど。コンテナIDは、状況によっては試料IDとは異なる場合があります。 / Id for container. There may be multiple; a manufacturer's bar code, lab assigned identifier, etc. The container ID may differ from the specimen id in some circumstances.</t>
   </si>
   <si>
     <t>SAC-3</t>
@@ -1566,7 +1566,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="40.65234375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="63.75390625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.6953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
